--- a/_Master_Data/item_master.xlsx
+++ b/_Master_Data/item_master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NSU_2027\Desktop\미국 공급망 고도화\1. 미국 주재원\비전2030(2026)\4.3.2 수요계획 강화\S&amp;OP\DashBoard 개발\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9425FBCD-765A-42DE-BAEB-D930AC48E855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BF22123-8CF9-43C3-843C-A5E9ADC3DB3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19788" yWindow="2124" windowWidth="17280" windowHeight="9960" xr2:uid="{2733CC6C-B9A5-4709-BFA1-FED732D53B09}"/>
+    <workbookView xWindow="5865" yWindow="3075" windowWidth="18750" windowHeight="11610" xr2:uid="{2733CC6C-B9A5-4709-BFA1-FED732D53B09}"/>
   </bookViews>
   <sheets>
     <sheet name="품목마스터" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">품목마스터!$A$1:$D$321</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">품목마스터!$A$1:$D$326</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="332">
   <si>
     <t>제품코드</t>
   </si>
@@ -1026,6 +1026,21 @@
   </si>
   <si>
     <t>RChef Garlic Chicken SF 16 (4x4) CAN</t>
+  </si>
+  <si>
+    <t>(E)K-Ramyun Best 4Mix 16(SOxSBxNSxC)</t>
+  </si>
+  <si>
+    <t>(E)Shin Chapa 2Mix 8(SOxC)</t>
+  </si>
+  <si>
+    <t>Dakdari Drumpops Original (66g) [TT]</t>
+  </si>
+  <si>
+    <t>Dakdari Drumpops Sweet&amp;Spicy (66g) [TT]</t>
+  </si>
+  <si>
+    <t>Big Bowl Shin Black 6</t>
   </si>
 </sst>
 </file>
@@ -1164,12 +1179,12 @@
       <sheetName val="계획 대비 실적(수입,스낵제외)"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
       <sheetData sheetId="6">
         <row r="2">
           <cell r="A2">
@@ -3625,11 +3640,11 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3952,7 +3967,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7D35813-652F-4AC0-875E-EDF683EA9BC1}">
-  <dimension ref="A1:D321"/>
+  <dimension ref="A1:D326"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="13.125" bestFit="1" customWidth="1"/>
@@ -8151,10 +8166,10 @@
     </row>
     <row r="288" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>101070203</v>
+        <v>101070197</v>
       </c>
       <c r="B288" s="4" t="s">
-        <v>286</v>
+        <v>327</v>
       </c>
       <c r="C288" s="6" t="s">
         <v>35</v>
@@ -8165,13 +8180,13 @@
     </row>
     <row r="289" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A289" s="4">
-        <v>101070204</v>
+        <v>101070203</v>
       </c>
       <c r="B289" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="C289" s="5" t="s">
-        <v>71</v>
+        <v>286</v>
+      </c>
+      <c r="C289" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="D289" t="s">
         <v>320</v>
@@ -8179,13 +8194,13 @@
     </row>
     <row r="290" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A290" s="4">
-        <v>101070205</v>
+        <v>101070204</v>
       </c>
       <c r="B290" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="C290" s="6" t="s">
-        <v>35</v>
+        <v>287</v>
+      </c>
+      <c r="C290" s="5" t="s">
+        <v>71</v>
       </c>
       <c r="D290" t="s">
         <v>320</v>
@@ -8193,13 +8208,13 @@
     </row>
     <row r="291" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A291" s="4">
-        <v>101070209</v>
+        <v>101070205</v>
       </c>
       <c r="B291" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="C291" s="5" t="s">
-        <v>71</v>
+        <v>288</v>
+      </c>
+      <c r="C291" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="D291" t="s">
         <v>320</v>
@@ -8207,13 +8222,13 @@
     </row>
     <row r="292" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A292" s="4">
-        <v>101070220</v>
+        <v>101070209</v>
       </c>
       <c r="B292" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="C292" s="6" t="s">
-        <v>35</v>
+        <v>289</v>
+      </c>
+      <c r="C292" s="5" t="s">
+        <v>71</v>
       </c>
       <c r="D292" t="s">
         <v>320</v>
@@ -8221,12 +8236,12 @@
     </row>
     <row r="293" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A293" s="4">
-        <v>101070221</v>
+        <v>101070220</v>
       </c>
       <c r="B293" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="C293" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="C293" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D293" t="s">
@@ -8235,83 +8250,83 @@
     </row>
     <row r="294" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A294" s="4">
+        <v>101070221</v>
+      </c>
+      <c r="B294" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C294" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D294" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A295" s="4">
+        <v>101070222</v>
+      </c>
+      <c r="B295" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="C295" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D295" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A296" s="4">
         <v>101070224</v>
       </c>
-      <c r="B294" s="4" t="s">
+      <c r="B296" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="C294" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D294" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="295" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A295" s="4">
+      <c r="C296" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D296" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A297" s="4">
         <v>101070232</v>
       </c>
-      <c r="B295" s="7" t="s">
+      <c r="B297" s="7" t="s">
         <v>325</v>
       </c>
-      <c r="C295" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D295" t="s">
+      <c r="C297" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D297" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="296" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A296" s="4">
+    <row r="298" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A298" s="4">
         <v>101070233</v>
       </c>
-      <c r="B296" s="7" t="s">
+      <c r="B298" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="C296" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D296" t="s">
+      <c r="C298" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D298" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="297" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A297" s="4">
-        <v>102000296</v>
-      </c>
-      <c r="B297" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="C297" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D297" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="298" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A298" s="4">
-        <v>102000334</v>
-      </c>
-      <c r="B298" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="C298" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D298" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="299" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A299" s="4">
-        <v>102001999</v>
-      </c>
-      <c r="B299" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="C299" s="5" t="s">
-        <v>71</v>
+        <v>101070237</v>
+      </c>
+      <c r="B299" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="C299" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="D299" t="s">
         <v>320</v>
@@ -8319,12 +8334,12 @@
     </row>
     <row r="300" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A300" s="4">
-        <v>102002142</v>
+        <v>102000296</v>
       </c>
       <c r="B300" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="C300" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="C300" s="6" t="s">
         <v>71</v>
       </c>
       <c r="D300" t="s">
@@ -8333,12 +8348,12 @@
     </row>
     <row r="301" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A301" s="4">
-        <v>102002753</v>
+        <v>102000334</v>
       </c>
       <c r="B301" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="C301" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="C301" s="6" t="s">
         <v>71</v>
       </c>
       <c r="D301" t="s">
@@ -8347,10 +8362,10 @@
     </row>
     <row r="302" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A302" s="4">
-        <v>102002755</v>
+        <v>102001999</v>
       </c>
       <c r="B302" s="4" t="s">
-        <v>324</v>
+        <v>295</v>
       </c>
       <c r="C302" s="5" t="s">
         <v>71</v>
@@ -8361,12 +8376,12 @@
     </row>
     <row r="303" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A303" s="4">
-        <v>102002772</v>
+        <v>102002142</v>
       </c>
       <c r="B303" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="C303" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="C303" s="5" t="s">
         <v>71</v>
       </c>
       <c r="D303" t="s">
@@ -8375,10 +8390,10 @@
     </row>
     <row r="304" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A304" s="4">
-        <v>102002773</v>
+        <v>102002753</v>
       </c>
       <c r="B304" s="4" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C304" s="5" t="s">
         <v>71</v>
@@ -8389,12 +8404,12 @@
     </row>
     <row r="305" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A305" s="4">
-        <v>102002774</v>
+        <v>102002755</v>
       </c>
       <c r="B305" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="C305" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="C305" s="5" t="s">
         <v>71</v>
       </c>
       <c r="D305" t="s">
@@ -8403,12 +8418,12 @@
     </row>
     <row r="306" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A306" s="4">
-        <v>102002775</v>
+        <v>102002772</v>
       </c>
       <c r="B306" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="C306" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="C306" s="6" t="s">
         <v>71</v>
       </c>
       <c r="D306" t="s">
@@ -8417,12 +8432,12 @@
     </row>
     <row r="307" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A307" s="4">
-        <v>102070038</v>
+        <v>102002773</v>
       </c>
       <c r="B307" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="C307" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="C307" s="5" t="s">
         <v>71</v>
       </c>
       <c r="D307" t="s">
@@ -8431,12 +8446,12 @@
     </row>
     <row r="308" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A308" s="4">
-        <v>102070041</v>
+        <v>102002774</v>
       </c>
       <c r="B308" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="C308" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="C308" s="6" t="s">
         <v>71</v>
       </c>
       <c r="D308" t="s">
@@ -8445,12 +8460,12 @@
     </row>
     <row r="309" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A309" s="4">
-        <v>102070042</v>
+        <v>102002775</v>
       </c>
       <c r="B309" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="C309" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="C309" s="5" t="s">
         <v>71</v>
       </c>
       <c r="D309" t="s">
@@ -8459,10 +8474,10 @@
     </row>
     <row r="310" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>102070043</v>
+        <v>102070016</v>
       </c>
       <c r="B310" s="4" t="s">
-        <v>305</v>
+        <v>329</v>
       </c>
       <c r="C310" s="5" t="s">
         <v>71</v>
@@ -8473,10 +8488,10 @@
     </row>
     <row r="311" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A311" s="4">
-        <v>901001521</v>
+        <v>102070020</v>
       </c>
       <c r="B311" s="4" t="s">
-        <v>306</v>
+        <v>330</v>
       </c>
       <c r="C311" s="5" t="s">
         <v>71</v>
@@ -8487,12 +8502,12 @@
     </row>
     <row r="312" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A312" s="4">
-        <v>901001941</v>
+        <v>102070038</v>
       </c>
       <c r="B312" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="C312" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="C312" s="6" t="s">
         <v>71</v>
       </c>
       <c r="D312" t="s">
@@ -8501,10 +8516,10 @@
     </row>
     <row r="313" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A313" s="4">
-        <v>901001955</v>
+        <v>102070041</v>
       </c>
       <c r="B313" s="4" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="C313" s="5" t="s">
         <v>71</v>
@@ -8515,12 +8530,12 @@
     </row>
     <row r="314" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A314" s="4">
-        <v>901001956</v>
+        <v>102070042</v>
       </c>
       <c r="B314" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="C314" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="C314" s="6" t="s">
         <v>71</v>
       </c>
       <c r="D314" t="s">
@@ -8529,10 +8544,10 @@
     </row>
     <row r="315" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A315" s="4">
-        <v>901001957</v>
+        <v>102070043</v>
       </c>
       <c r="B315" s="4" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="C315" s="5" t="s">
         <v>71</v>
@@ -8543,10 +8558,10 @@
     </row>
     <row r="316" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A316" s="4">
-        <v>901001961</v>
+        <v>901001521</v>
       </c>
       <c r="B316" s="4" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="C316" s="5" t="s">
         <v>71</v>
@@ -8557,10 +8572,10 @@
     </row>
     <row r="317" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A317" s="4">
-        <v>901001964</v>
+        <v>901001941</v>
       </c>
       <c r="B317" s="4" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="C317" s="5" t="s">
         <v>71</v>
@@ -8571,10 +8586,10 @@
     </row>
     <row r="318" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A318" s="4">
-        <v>902000771</v>
+        <v>901001955</v>
       </c>
       <c r="B318" s="4" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="C318" s="5" t="s">
         <v>71</v>
@@ -8585,10 +8600,10 @@
     </row>
     <row r="319" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A319" s="4">
-        <v>902070007</v>
+        <v>901001956</v>
       </c>
       <c r="B319" s="4" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="C319" s="5" t="s">
         <v>71</v>
@@ -8599,10 +8614,10 @@
     </row>
     <row r="320" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A320" s="4">
-        <v>903000582</v>
+        <v>901001957</v>
       </c>
       <c r="B320" s="4" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="C320" s="5" t="s">
         <v>71</v>
@@ -8611,12 +8626,12 @@
         <v>320</v>
       </c>
     </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="321" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>903070001</v>
+        <v>901001961</v>
       </c>
       <c r="B321" s="4" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="C321" s="5" t="s">
         <v>71</v>
@@ -8625,8 +8640,78 @@
         <v>320</v>
       </c>
     </row>
+    <row r="322" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A322" s="4">
+        <v>901001964</v>
+      </c>
+      <c r="B322" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="C322" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D322" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A323" s="4">
+        <v>902000771</v>
+      </c>
+      <c r="B323" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="C323" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D323" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A324" s="4">
+        <v>902070007</v>
+      </c>
+      <c r="B324" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="C324" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D324" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A325" s="4">
+        <v>903000582</v>
+      </c>
+      <c r="B325" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="C325" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D325" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A326" s="4">
+        <v>903070001</v>
+      </c>
+      <c r="B326" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="C326" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D326" t="s">
+        <v>320</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D321" xr:uid="{D7D35813-652F-4AC0-875E-EDF683EA9BC1}"/>
+  <autoFilter ref="A1:D326" xr:uid="{D7D35813-652F-4AC0-875E-EDF683EA9BC1}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>